--- a/meta/stores/PageTransitDataStore.xlsx
+++ b/meta/stores/PageTransitDataStore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10709"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tueda/data/webstorm/dapanda/dapanda-front-core/meta/stores/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taihei\develop\project\ueoware\repos\dapanda-front-core\meta\stores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698AAE3D-BA42-6D43-A956-4DFC0467F430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8674B1-55EA-4CE5-BD6B-D6486E8815FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11300" yWindow="4460" windowWidth="28800" windowHeight="17500" tabRatio="640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10500" yWindow="1116" windowWidth="15900" windowHeight="13776" tabRatio="640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VueStore" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="97">
   <si>
     <t>パッケージ</t>
   </si>
@@ -805,12 +805,24 @@
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>transit</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>boolean</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ページ遷移を検知するためのtoggleスイッチです。</t>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1725,50 +1737,50 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2182,19 +2194,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K155"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
-    <col min="2" max="5" width="23.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" style="1" customWidth="1"/>
+    <col min="2" max="5" width="23.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.77734375" style="1" customWidth="1"/>
     <col min="9" max="9" width="28" style="1" customWidth="1"/>
     <col min="10" max="10" width="33.33203125" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19">
+    <row r="1" spans="1:10" ht="19.2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>32</v>
       </c>
@@ -2202,17 +2214,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
@@ -2221,7 +2233,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>36</v>
       </c>
@@ -2235,7 +2247,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
@@ -2249,11 +2261,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="106" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="107"/>
+      <c r="B8" s="108"/>
       <c r="C8" s="10" t="s">
         <v>20</v>
       </c>
@@ -2263,11 +2275,11 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="106" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="107"/>
+      <c r="B9" s="108"/>
       <c r="C9" s="73" t="s">
         <v>30</v>
       </c>
@@ -2277,19 +2289,19 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="45" customHeight="1">
+    <row r="10" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B10" s="6"/>
-      <c r="C10" s="108" t="s">
+      <c r="C10" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="109"/>
-      <c r="E10" s="110"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="111"/>
       <c r="F10" s="56"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>2</v>
       </c>
@@ -2300,7 +2312,7 @@
       <c r="D11" s="12"/>
       <c r="E11" s="8"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="54" t="s">
         <v>15</v>
       </c>
@@ -2313,11 +2325,11 @@
       <c r="F12"/>
       <c r="G12"/>
     </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="111" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="112"/>
+      <c r="B13" s="113"/>
       <c r="C13" s="55" t="s">
         <v>14</v>
       </c>
@@ -2328,10 +2340,10 @@
       <c r="F13"/>
       <c r="G13"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="29" t="s">
         <v>49</v>
       </c>
@@ -2343,7 +2355,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="39" t="s">
         <v>7</v>
       </c>
@@ -2358,7 +2370,7 @@
       <c r="I16" s="37"/>
       <c r="J16" s="37"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="43">
         <v>1</v>
       </c>
@@ -2373,7 +2385,7 @@
       <c r="I17"/>
       <c r="J17"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="43">
         <v>2</v>
       </c>
@@ -2388,7 +2400,7 @@
       <c r="I18"/>
       <c r="J18"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="43"/>
       <c r="B19" s="38"/>
       <c r="C19" s="34"/>
@@ -2399,7 +2411,7 @@
       <c r="I19"/>
       <c r="J19"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="44"/>
       <c r="B20" s="40"/>
       <c r="C20" s="41"/>
@@ -2410,7 +2422,7 @@
       <c r="I20"/>
       <c r="J20"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
@@ -2420,7 +2432,7 @@
       <c r="G21"/>
       <c r="H21"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
@@ -2430,7 +2442,7 @@
       <c r="G22"/>
       <c r="H22"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23"/>
       <c r="B23" t="s">
         <v>41</v>
@@ -2442,7 +2454,7 @@
       <c r="G23"/>
       <c r="H23"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>46</v>
       </c>
@@ -2457,47 +2469,47 @@
       <c r="J24" s="6"/>
       <c r="K24" s="14"/>
     </row>
-    <row r="25" spans="1:11" ht="13.5" customHeight="1">
+    <row r="25" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="97" t="s">
         <v>7</v>
       </c>
       <c r="B25" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="105" t="s">
+      <c r="C25" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="105" t="s">
+      <c r="D25" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="105" t="s">
+      <c r="E25" s="104" t="s">
         <v>5</v>
       </c>
       <c r="F25" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="G25" s="105" t="s">
+      <c r="G25" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="H25" s="105"/>
+      <c r="H25" s="104"/>
       <c r="I25" s="15"/>
       <c r="J25" s="16"/>
       <c r="K25" s="9"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="97"/>
       <c r="B26" s="97"/>
-      <c r="C26" s="105"/>
-      <c r="D26" s="105"/>
-      <c r="E26" s="105"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="104"/>
+      <c r="E26" s="104"/>
       <c r="F26" s="94"/>
-      <c r="G26" s="105"/>
-      <c r="H26" s="105"/>
+      <c r="G26" s="104"/>
+      <c r="H26" s="104"/>
       <c r="I26" s="17"/>
       <c r="J26" s="28"/>
       <c r="K26" s="14"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="18">
         <v>1</v>
       </c>
@@ -2520,7 +2532,7 @@
       <c r="J27" s="27"/>
       <c r="K27" s="14"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="18">
         <f>A27+1</f>
         <v>2</v>
@@ -2544,7 +2556,7 @@
       <c r="J28" s="27"/>
       <c r="K28" s="14"/>
     </row>
-    <row r="29" spans="1:11" ht="150" customHeight="1">
+    <row r="29" spans="1:11" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="18">
         <f t="shared" ref="A29:A34" si="0">A28+1</f>
         <v>3</v>
@@ -2560,15 +2572,15 @@
         <v>73</v>
       </c>
       <c r="F29" s="19"/>
-      <c r="G29" s="113" t="s">
+      <c r="G29" s="101" t="s">
         <v>75</v>
       </c>
-      <c r="H29" s="114"/>
-      <c r="I29" s="114"/>
-      <c r="J29" s="115"/>
+      <c r="H29" s="102"/>
+      <c r="I29" s="102"/>
+      <c r="J29" s="103"/>
       <c r="K29" s="14"/>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="18">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2592,7 +2604,7 @@
       <c r="J30" s="67"/>
       <c r="K30" s="14"/>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="18">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2616,7 +2628,7 @@
       <c r="J31" s="67"/>
       <c r="K31" s="14"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="18">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2640,23 +2652,31 @@
       <c r="J32" s="21"/>
       <c r="K32" s="14"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="18">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B33" s="63"/>
-      <c r="C33" s="70"/>
+      <c r="B33" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="70" t="s">
+        <v>95</v>
+      </c>
       <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
+      <c r="E33" s="19" t="b">
+        <v>0</v>
+      </c>
       <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
+      <c r="G33" s="19" t="s">
+        <v>96</v>
+      </c>
       <c r="H33" s="20"/>
       <c r="I33" s="20"/>
       <c r="J33" s="21"/>
       <c r="K33" s="14"/>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="18">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2672,7 +2692,7 @@
       <c r="J34" s="67"/>
       <c r="K34" s="14"/>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="22"/>
       <c r="B35" s="23"/>
       <c r="C35" s="24"/>
@@ -2685,7 +2705,7 @@
       <c r="J35" s="26"/>
       <c r="K35" s="14"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="29" t="s">
         <v>50</v>
       </c>
@@ -2697,7 +2717,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="39" t="s">
         <v>7</v>
       </c>
@@ -2712,7 +2732,7 @@
       <c r="I39" s="37"/>
       <c r="J39" s="37"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="43"/>
       <c r="B40" s="38"/>
       <c r="C40" s="32"/>
@@ -2723,7 +2743,7 @@
       <c r="I40"/>
       <c r="J40"/>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="43"/>
       <c r="B41" s="38"/>
       <c r="C41" s="34"/>
@@ -2734,7 +2754,7 @@
       <c r="I41"/>
       <c r="J41"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="44"/>
       <c r="B42" s="40"/>
       <c r="C42" s="41"/>
@@ -2745,7 +2765,7 @@
       <c r="I42"/>
       <c r="J42"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
@@ -2755,7 +2775,7 @@
       <c r="G43"/>
       <c r="H43"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44"/>
       <c r="B44"/>
       <c r="C44"/>
@@ -2765,7 +2785,7 @@
       <c r="G44"/>
       <c r="H44"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45"/>
       <c r="B45" t="s">
         <v>42</v>
@@ -2777,7 +2797,7 @@
       <c r="G45"/>
       <c r="H45"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>45</v>
       </c>
@@ -2792,7 +2812,7 @@
       <c r="J46" s="6"/>
       <c r="K46" s="14"/>
     </row>
-    <row r="47" spans="1:11" ht="13.5" customHeight="1">
+    <row r="47" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="97" t="s">
         <v>7</v>
       </c>
@@ -2803,32 +2823,32 @@
         <v>4</v>
       </c>
       <c r="D47" s="98"/>
-      <c r="E47" s="105" t="s">
+      <c r="E47" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="F47" s="103"/>
-      <c r="G47" s="105" t="s">
+      <c r="F47" s="105"/>
+      <c r="G47" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="H47" s="105"/>
+      <c r="H47" s="104"/>
       <c r="I47" s="15"/>
       <c r="J47" s="16"/>
       <c r="K47" s="9"/>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="97"/>
       <c r="B48" s="97"/>
       <c r="C48" s="96"/>
       <c r="D48" s="99"/>
-      <c r="E48" s="105"/>
-      <c r="F48" s="104"/>
-      <c r="G48" s="105"/>
-      <c r="H48" s="105"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="106"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="104"/>
       <c r="I48" s="17"/>
       <c r="J48" s="28"/>
       <c r="K48" s="14"/>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="18">
         <v>1</v>
       </c>
@@ -2843,7 +2863,7 @@
       <c r="J49" s="27"/>
       <c r="K49" s="14"/>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="18">
         <f>A49+1</f>
         <v>2</v>
@@ -2859,7 +2879,7 @@
       <c r="J50" s="27"/>
       <c r="K50" s="14"/>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="18">
         <f t="shared" ref="A51:A54" si="1">A50+1</f>
         <v>3</v>
@@ -2875,7 +2895,7 @@
       <c r="J51" s="21"/>
       <c r="K51" s="14"/>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="18">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -2891,7 +2911,7 @@
       <c r="J52" s="21"/>
       <c r="K52" s="14"/>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="18">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -2907,7 +2927,7 @@
       <c r="J53" s="21"/>
       <c r="K53" s="14"/>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="18">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -2923,7 +2943,7 @@
       <c r="J54" s="67"/>
       <c r="K54" s="14"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="22"/>
       <c r="B55" s="23"/>
       <c r="C55" s="24"/>
@@ -2936,7 +2956,7 @@
       <c r="J55" s="26"/>
       <c r="K55" s="14"/>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58"/>
       <c r="B58" t="s">
         <v>42</v>
@@ -2948,7 +2968,7 @@
       <c r="G58"/>
       <c r="H58"/>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>45</v>
       </c>
@@ -2963,7 +2983,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="14"/>
     </row>
-    <row r="60" spans="1:11" ht="13.5" customHeight="1">
+    <row r="60" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="97" t="s">
         <v>7</v>
       </c>
@@ -2974,32 +2994,32 @@
         <v>4</v>
       </c>
       <c r="D60" s="98"/>
-      <c r="E60" s="105" t="s">
+      <c r="E60" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="F60" s="103"/>
-      <c r="G60" s="105" t="s">
+      <c r="F60" s="105"/>
+      <c r="G60" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="H60" s="105"/>
+      <c r="H60" s="104"/>
       <c r="I60" s="15"/>
       <c r="J60" s="16"/>
       <c r="K60" s="9"/>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="97"/>
       <c r="B61" s="97"/>
       <c r="C61" s="96"/>
       <c r="D61" s="99"/>
-      <c r="E61" s="105"/>
-      <c r="F61" s="104"/>
-      <c r="G61" s="105"/>
-      <c r="H61" s="105"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="106"/>
+      <c r="G61" s="104"/>
+      <c r="H61" s="104"/>
       <c r="I61" s="17"/>
       <c r="J61" s="28"/>
       <c r="K61" s="14"/>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="18">
         <v>1</v>
       </c>
@@ -3014,7 +3034,7 @@
       <c r="J62" s="27"/>
       <c r="K62" s="14"/>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="18">
         <f>A62+1</f>
         <v>2</v>
@@ -3030,7 +3050,7 @@
       <c r="J63" s="27"/>
       <c r="K63" s="14"/>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="18">
         <f t="shared" ref="A64:A67" si="2">A63+1</f>
         <v>3</v>
@@ -3046,7 +3066,7 @@
       <c r="J64" s="21"/>
       <c r="K64" s="14"/>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="18">
         <f t="shared" si="2"/>
         <v>4</v>
@@ -3062,7 +3082,7 @@
       <c r="J65" s="21"/>
       <c r="K65" s="14"/>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="18">
         <f t="shared" si="2"/>
         <v>5</v>
@@ -3078,7 +3098,7 @@
       <c r="J66" s="21"/>
       <c r="K66" s="14"/>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="18">
         <f t="shared" si="2"/>
         <v>6</v>
@@ -3094,7 +3114,7 @@
       <c r="J67" s="67"/>
       <c r="K67" s="14"/>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="22"/>
       <c r="B68" s="23"/>
       <c r="C68" s="24"/>
@@ -3107,7 +3127,7 @@
       <c r="J68" s="26"/>
       <c r="K68" s="14"/>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="29" t="s">
         <v>51</v>
       </c>
@@ -3119,7 +3139,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="39" t="s">
         <v>7</v>
       </c>
@@ -3134,7 +3154,7 @@
       <c r="I72" s="37"/>
       <c r="J72" s="37"/>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="43">
         <v>1</v>
       </c>
@@ -3149,7 +3169,7 @@
       <c r="I73"/>
       <c r="J73"/>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="43">
         <v>2</v>
       </c>
@@ -3164,7 +3184,7 @@
       <c r="I74"/>
       <c r="J74"/>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="43"/>
       <c r="B75" s="38"/>
       <c r="C75" s="34"/>
@@ -3175,7 +3195,7 @@
       <c r="I75"/>
       <c r="J75"/>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="44"/>
       <c r="B76" s="40"/>
       <c r="C76" s="41"/>
@@ -3186,7 +3206,7 @@
       <c r="I76"/>
       <c r="J76"/>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77"/>
       <c r="B77"/>
       <c r="C77"/>
@@ -3196,7 +3216,7 @@
       <c r="G77"/>
       <c r="H77"/>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78"/>
       <c r="B78"/>
       <c r="C78"/>
@@ -3206,7 +3226,7 @@
       <c r="G78"/>
       <c r="H78"/>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79"/>
       <c r="B79" t="s">
         <v>43</v>
@@ -3218,7 +3238,7 @@
       <c r="G79"/>
       <c r="H79"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
         <v>44</v>
       </c>
@@ -3233,17 +3253,17 @@
       <c r="J80" s="6"/>
       <c r="K80" s="14"/>
     </row>
-    <row r="81" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A81" s="101" t="s">
+    <row r="81" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="B81" s="101" t="s">
+      <c r="B81" s="114" t="s">
         <v>3</v>
       </c>
       <c r="C81" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="D81" s="103"/>
+      <c r="D81" s="105"/>
       <c r="E81" s="93" t="s">
         <v>6</v>
       </c>
@@ -3260,11 +3280,11 @@
       <c r="J81" s="16"/>
       <c r="K81" s="9"/>
     </row>
-    <row r="82" spans="1:11">
-      <c r="A82" s="102"/>
-      <c r="B82" s="102"/>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A82" s="115"/>
+      <c r="B82" s="115"/>
       <c r="C82" s="96"/>
-      <c r="D82" s="104"/>
+      <c r="D82" s="106"/>
       <c r="E82" s="94"/>
       <c r="F82" s="94"/>
       <c r="G82" s="94"/>
@@ -3273,7 +3293,7 @@
       <c r="J82" s="28"/>
       <c r="K82" s="14"/>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="18">
         <v>1</v>
       </c>
@@ -3294,7 +3314,7 @@
       <c r="J83" s="27"/>
       <c r="K83" s="14"/>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="18">
         <f>A83+1</f>
         <v>2</v>
@@ -3314,7 +3334,7 @@
       <c r="J84" s="27"/>
       <c r="K84" s="14"/>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="18">
         <f t="shared" ref="A85:A89" si="3">A84+1</f>
         <v>3</v>
@@ -3336,7 +3356,7 @@
       <c r="J85" s="21"/>
       <c r="K85" s="14"/>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="18">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -3360,7 +3380,7 @@
       <c r="J86" s="21"/>
       <c r="K86" s="14"/>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="18">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -3382,7 +3402,7 @@
       <c r="J87" s="21"/>
       <c r="K87" s="14"/>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="18">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -3398,7 +3418,7 @@
       <c r="J88" s="67"/>
       <c r="K88" s="14"/>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="18">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -3414,7 +3434,7 @@
       <c r="J89" s="67"/>
       <c r="K89" s="14"/>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="22"/>
       <c r="B90" s="23"/>
       <c r="C90" s="24"/>
@@ -3427,7 +3447,7 @@
       <c r="J90" s="26"/>
       <c r="K90" s="14"/>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93"/>
       <c r="B93" t="s">
         <v>43</v>
@@ -3439,7 +3459,7 @@
       <c r="G93"/>
       <c r="H93"/>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="3" t="s">
         <v>44</v>
       </c>
@@ -3454,7 +3474,7 @@
       <c r="J94" s="6"/>
       <c r="K94" s="14"/>
     </row>
-    <row r="95" spans="1:11" ht="13.5" customHeight="1">
+    <row r="95" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="97" t="s">
         <v>7</v>
       </c>
@@ -3481,7 +3501,7 @@
       <c r="J95" s="16"/>
       <c r="K95" s="9"/>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="97"/>
       <c r="B96" s="97"/>
       <c r="C96" s="96"/>
@@ -3494,7 +3514,7 @@
       <c r="J96" s="28"/>
       <c r="K96" s="14"/>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="18">
         <v>1</v>
       </c>
@@ -3517,7 +3537,7 @@
       <c r="J97" s="27"/>
       <c r="K97" s="14"/>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="18">
         <f>A97+1</f>
         <v>2</v>
@@ -3539,7 +3559,7 @@
       <c r="J98" s="27"/>
       <c r="K98" s="14"/>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="18">
         <f t="shared" ref="A99:A102" si="4">A98+1</f>
         <v>3</v>
@@ -3555,7 +3575,7 @@
       <c r="J99" s="21"/>
       <c r="K99" s="14"/>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="18">
         <f t="shared" si="4"/>
         <v>4</v>
@@ -3577,7 +3597,7 @@
       <c r="J100" s="21"/>
       <c r="K100" s="14"/>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="18">
         <f t="shared" si="4"/>
         <v>5</v>
@@ -3593,7 +3613,7 @@
       <c r="J101" s="21"/>
       <c r="K101" s="14"/>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="18">
         <f t="shared" si="4"/>
         <v>6</v>
@@ -3609,7 +3629,7 @@
       <c r="J102" s="67"/>
       <c r="K102" s="14"/>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="22"/>
       <c r="B103" s="23"/>
       <c r="C103" s="24"/>
@@ -3622,7 +3642,7 @@
       <c r="J103" s="26"/>
       <c r="K103" s="14"/>
     </row>
-    <row r="106" spans="1:11">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106"/>
       <c r="B106" t="s">
         <v>43</v>
@@ -3634,7 +3654,7 @@
       <c r="G106"/>
       <c r="H106"/>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
         <v>44</v>
       </c>
@@ -3649,7 +3669,7 @@
       <c r="J107" s="6"/>
       <c r="K107" s="14"/>
     </row>
-    <row r="108" spans="1:11" ht="13.5" customHeight="1">
+    <row r="108" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="97" t="s">
         <v>7</v>
       </c>
@@ -3676,7 +3696,7 @@
       <c r="J108" s="16"/>
       <c r="K108" s="9"/>
     </row>
-    <row r="109" spans="1:11">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" s="97"/>
       <c r="B109" s="97"/>
       <c r="C109" s="96"/>
@@ -3689,7 +3709,7 @@
       <c r="J109" s="28"/>
       <c r="K109" s="14"/>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="18">
         <v>1</v>
       </c>
@@ -3710,7 +3730,7 @@
       <c r="J110" s="27"/>
       <c r="K110" s="14"/>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="18">
         <f>A110+1</f>
         <v>2</v>
@@ -3734,7 +3754,7 @@
       <c r="J111" s="27"/>
       <c r="K111" s="14"/>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="18">
         <f t="shared" ref="A112:A115" si="5">A111+1</f>
         <v>3</v>
@@ -3758,7 +3778,7 @@
       <c r="J112" s="21"/>
       <c r="K112" s="14"/>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="18">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -3774,7 +3794,7 @@
       <c r="J113" s="21"/>
       <c r="K113" s="14"/>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="18">
         <f t="shared" si="5"/>
         <v>5</v>
@@ -3790,7 +3810,7 @@
       <c r="J114" s="21"/>
       <c r="K114" s="14"/>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="18">
         <f t="shared" si="5"/>
         <v>6</v>
@@ -3806,7 +3826,7 @@
       <c r="J115" s="67"/>
       <c r="K115" s="14"/>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="22"/>
       <c r="B116" s="23"/>
       <c r="C116" s="24"/>
@@ -3819,7 +3839,7 @@
       <c r="J116" s="26"/>
       <c r="K116" s="14"/>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119"/>
       <c r="B119" t="s">
         <v>43</v>
@@ -3831,7 +3851,7 @@
       <c r="G119"/>
       <c r="H119"/>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
         <v>44</v>
       </c>
@@ -3846,7 +3866,7 @@
       <c r="J120" s="6"/>
       <c r="K120" s="14"/>
     </row>
-    <row r="121" spans="1:11" ht="13.5" customHeight="1">
+    <row r="121" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="97" t="s">
         <v>7</v>
       </c>
@@ -3873,7 +3893,7 @@
       <c r="J121" s="16"/>
       <c r="K121" s="9"/>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="97"/>
       <c r="B122" s="97"/>
       <c r="C122" s="96"/>
@@ -3886,7 +3906,7 @@
       <c r="J122" s="28"/>
       <c r="K122" s="14"/>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="18">
         <v>1</v>
       </c>
@@ -3909,7 +3929,7 @@
       <c r="J123" s="27"/>
       <c r="K123" s="14"/>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="18">
         <f>A123+1</f>
         <v>2</v>
@@ -3931,7 +3951,7 @@
       <c r="J124" s="27"/>
       <c r="K124" s="14"/>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="18">
         <f t="shared" ref="A125:A128" si="6">A124+1</f>
         <v>3</v>
@@ -3947,7 +3967,7 @@
       <c r="J125" s="21"/>
       <c r="K125" s="14"/>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="18">
         <f t="shared" si="6"/>
         <v>4</v>
@@ -3963,7 +3983,7 @@
       <c r="J126" s="21"/>
       <c r="K126" s="14"/>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="18">
         <f t="shared" si="6"/>
         <v>5</v>
@@ -3979,7 +3999,7 @@
       <c r="J127" s="21"/>
       <c r="K127" s="14"/>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="18">
         <f t="shared" si="6"/>
         <v>6</v>
@@ -3995,7 +4015,7 @@
       <c r="J128" s="67"/>
       <c r="K128" s="14"/>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="22"/>
       <c r="B129" s="23"/>
       <c r="C129" s="24"/>
@@ -4008,7 +4028,7 @@
       <c r="J129" s="26"/>
       <c r="K129" s="14"/>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132"/>
       <c r="B132" t="s">
         <v>43</v>
@@ -4020,7 +4040,7 @@
       <c r="G132"/>
       <c r="H132"/>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
         <v>44</v>
       </c>
@@ -4035,7 +4055,7 @@
       <c r="J133" s="6"/>
       <c r="K133" s="14"/>
     </row>
-    <row r="134" spans="1:11" ht="13.5" customHeight="1">
+    <row r="134" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="97" t="s">
         <v>7</v>
       </c>
@@ -4062,7 +4082,7 @@
       <c r="J134" s="16"/>
       <c r="K134" s="9"/>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="97"/>
       <c r="B135" s="97"/>
       <c r="C135" s="96"/>
@@ -4075,7 +4095,7 @@
       <c r="J135" s="28"/>
       <c r="K135" s="14"/>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="18">
         <v>1</v>
       </c>
@@ -4096,7 +4116,7 @@
       <c r="J136" s="27"/>
       <c r="K136" s="14"/>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="18">
         <f>A136+1</f>
         <v>2</v>
@@ -4118,7 +4138,7 @@
       <c r="J137" s="27"/>
       <c r="K137" s="14"/>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="18">
         <f t="shared" ref="A138:A141" si="7">A137+1</f>
         <v>3</v>
@@ -4140,7 +4160,7 @@
       <c r="J138" s="21"/>
       <c r="K138" s="14"/>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="18">
         <f t="shared" si="7"/>
         <v>4</v>
@@ -4156,7 +4176,7 @@
       <c r="J139" s="21"/>
       <c r="K139" s="14"/>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="18">
         <f t="shared" si="7"/>
         <v>5</v>
@@ -4172,7 +4192,7 @@
       <c r="J140" s="21"/>
       <c r="K140" s="14"/>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="18">
         <f t="shared" si="7"/>
         <v>6</v>
@@ -4188,7 +4208,7 @@
       <c r="J141" s="67"/>
       <c r="K141" s="14"/>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="22"/>
       <c r="B142" s="23"/>
       <c r="C142" s="24"/>
@@ -4201,7 +4221,7 @@
       <c r="J142" s="26"/>
       <c r="K142" s="14"/>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145"/>
       <c r="B145" t="s">
         <v>43</v>
@@ -4213,7 +4233,7 @@
       <c r="G145"/>
       <c r="H145"/>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
         <v>44</v>
       </c>
@@ -4228,7 +4248,7 @@
       <c r="J146" s="6"/>
       <c r="K146" s="14"/>
     </row>
-    <row r="147" spans="1:11" ht="13.5" customHeight="1">
+    <row r="147" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="97" t="s">
         <v>7</v>
       </c>
@@ -4255,7 +4275,7 @@
       <c r="J147" s="16"/>
       <c r="K147" s="9"/>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" s="97"/>
       <c r="B148" s="97"/>
       <c r="C148" s="96"/>
@@ -4268,7 +4288,7 @@
       <c r="J148" s="28"/>
       <c r="K148" s="14"/>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" s="18">
         <v>1</v>
       </c>
@@ -4289,7 +4309,7 @@
       <c r="J149" s="27"/>
       <c r="K149" s="14"/>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" s="18">
         <f>A149+1</f>
         <v>2</v>
@@ -4311,7 +4331,7 @@
       <c r="J150" s="27"/>
       <c r="K150" s="14"/>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" s="18">
         <f t="shared" ref="A151:A154" si="8">A150+1</f>
         <v>3</v>
@@ -4327,7 +4347,7 @@
       <c r="J151" s="21"/>
       <c r="K151" s="14"/>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" s="18">
         <f t="shared" si="8"/>
         <v>4</v>
@@ -4343,7 +4363,7 @@
       <c r="J152" s="21"/>
       <c r="K152" s="14"/>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" s="18">
         <f t="shared" si="8"/>
         <v>5</v>
@@ -4359,7 +4379,7 @@
       <c r="J153" s="21"/>
       <c r="K153" s="14"/>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" s="18">
         <f t="shared" si="8"/>
         <v>6</v>
@@ -4375,7 +4395,7 @@
       <c r="J154" s="67"/>
       <c r="K154" s="14"/>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" s="22"/>
       <c r="B155" s="23"/>
       <c r="C155" s="24"/>
@@ -4390,13 +4410,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="G134:G135"/>
-    <mergeCell ref="H134:H135"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="C134:D135"/>
-    <mergeCell ref="E134:E135"/>
-    <mergeCell ref="F134:F135"/>
+    <mergeCell ref="G147:G148"/>
+    <mergeCell ref="H147:H148"/>
+    <mergeCell ref="A147:A148"/>
+    <mergeCell ref="B147:B148"/>
+    <mergeCell ref="C147:D148"/>
+    <mergeCell ref="E147:E148"/>
+    <mergeCell ref="F147:F148"/>
+    <mergeCell ref="G81:G82"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="G95:G96"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:D109"/>
+    <mergeCell ref="E108:E109"/>
+    <mergeCell ref="F108:F109"/>
+    <mergeCell ref="G108:G109"/>
+    <mergeCell ref="H108:H109"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:D82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="F81:F82"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:D96"/>
+    <mergeCell ref="E95:E96"/>
+    <mergeCell ref="F95:F96"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="G25:H26"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="F25:F26"/>
     <mergeCell ref="G29:J29"/>
     <mergeCell ref="A121:A122"/>
     <mergeCell ref="B121:B122"/>
@@ -4413,49 +4469,13 @@
     <mergeCell ref="C47:D48"/>
     <mergeCell ref="F47:F48"/>
     <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="G25:H26"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:D96"/>
-    <mergeCell ref="E95:E96"/>
-    <mergeCell ref="F95:F96"/>
-    <mergeCell ref="G81:G82"/>
-    <mergeCell ref="H81:H82"/>
-    <mergeCell ref="G95:G96"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:D109"/>
-    <mergeCell ref="E108:E109"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="G108:G109"/>
-    <mergeCell ref="H108:H109"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:D82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="F81:F82"/>
-    <mergeCell ref="G147:G148"/>
-    <mergeCell ref="H147:H148"/>
-    <mergeCell ref="A147:A148"/>
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="C147:D148"/>
-    <mergeCell ref="E147:E148"/>
-    <mergeCell ref="F147:F148"/>
+    <mergeCell ref="G134:G135"/>
+    <mergeCell ref="H134:H135"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C134:D135"/>
+    <mergeCell ref="E134:E135"/>
+    <mergeCell ref="F134:F135"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <dataValidations count="3">
@@ -4483,21 +4503,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="8.83203125" style="47" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" style="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" style="47" customWidth="1"/>
-    <col min="6" max="6" width="18.5" style="47" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" style="47" customWidth="1"/>
+    <col min="1" max="3" width="8.77734375" style="47" customWidth="1"/>
+    <col min="4" max="4" width="9.77734375" style="47" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" style="47" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" style="47" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" style="47" customWidth="1"/>
     <col min="8" max="8" width="18.6640625" style="47" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" style="47" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" style="47" customWidth="1"/>
     <col min="10" max="10" width="18.6640625" style="47" bestFit="1" customWidth="1"/>
-    <col min="11" max="251" width="8.83203125" style="47" customWidth="1"/>
-    <col min="252" max="16384" width="10.83203125" style="47"/>
+    <col min="11" max="251" width="8.77734375" style="47" customWidth="1"/>
+    <col min="252" max="16384" width="10.77734375" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19">
+    <row r="1" spans="1:10" ht="19.2" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>8</v>
       </c>
@@ -4513,7 +4533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B3" s="48" t="s">
         <v>21</v>
       </c>
@@ -4530,7 +4550,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="49" t="s">
         <v>22</v>
       </c>
@@ -4541,7 +4561,7 @@
       <c r="H4" s="50"/>
       <c r="J4" s="50"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="51" t="s">
         <v>23</v>
       </c>
@@ -4556,7 +4576,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="53"/>
     </row>
   </sheetData>

--- a/meta/stores/PageTransitDataStore.xlsx
+++ b/meta/stores/PageTransitDataStore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taihei\develop\project\ueoware\repos\dapanda-front-core\meta\stores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8674B1-55EA-4CE5-BD6B-D6486E8815FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5DF32F-DBA2-466D-9D65-27447D32DD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10500" yWindow="1116" windowWidth="15900" windowHeight="13776" tabRatio="640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22548" windowHeight="11400" tabRatio="640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VueStore" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="98">
   <si>
     <t>パッケージ</t>
   </si>
@@ -815,6 +815,10 @@
   </si>
   <si>
     <t>ページ遷移を検知するためのtoggleスイッチです。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>setLocation</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1737,6 +1741,42 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1745,42 +1785,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2193,7 +2197,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K155"/>
+  <dimension ref="A1:K169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -2262,10 +2266,10 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="107" t="s">
+      <c r="A8" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="108"/>
+      <c r="B8" s="107"/>
       <c r="C8" s="10" t="s">
         <v>20</v>
       </c>
@@ -2276,10 +2280,10 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="107" t="s">
+      <c r="A9" s="106" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="108"/>
+      <c r="B9" s="107"/>
       <c r="C9" s="73" t="s">
         <v>30</v>
       </c>
@@ -2294,11 +2298,11 @@
         <v>1</v>
       </c>
       <c r="B10" s="6"/>
-      <c r="C10" s="109" t="s">
+      <c r="C10" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="110"/>
-      <c r="E10" s="111"/>
+      <c r="D10" s="109"/>
+      <c r="E10" s="110"/>
       <c r="F10" s="56"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -2326,10 +2330,10 @@
       <c r="G12"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="112" t="s">
+      <c r="A13" s="111" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="113"/>
+      <c r="B13" s="112"/>
       <c r="C13" s="55" t="s">
         <v>14</v>
       </c>
@@ -2476,22 +2480,22 @@
       <c r="B25" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="104" t="s">
+      <c r="C25" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="104" t="s">
+      <c r="D25" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E25" s="104" t="s">
+      <c r="E25" s="105" t="s">
         <v>5</v>
       </c>
       <c r="F25" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="G25" s="104" t="s">
+      <c r="G25" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="H25" s="104"/>
+      <c r="H25" s="105"/>
       <c r="I25" s="15"/>
       <c r="J25" s="16"/>
       <c r="K25" s="9"/>
@@ -2499,12 +2503,12 @@
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="97"/>
       <c r="B26" s="97"/>
-      <c r="C26" s="104"/>
-      <c r="D26" s="104"/>
-      <c r="E26" s="104"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
       <c r="F26" s="94"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="104"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="105"/>
       <c r="I26" s="17"/>
       <c r="J26" s="28"/>
       <c r="K26" s="14"/>
@@ -2572,12 +2576,12 @@
         <v>73</v>
       </c>
       <c r="F29" s="19"/>
-      <c r="G29" s="101" t="s">
+      <c r="G29" s="113" t="s">
         <v>75</v>
       </c>
-      <c r="H29" s="102"/>
-      <c r="I29" s="102"/>
-      <c r="J29" s="103"/>
+      <c r="H29" s="114"/>
+      <c r="I29" s="114"/>
+      <c r="J29" s="115"/>
       <c r="K29" s="14"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
@@ -2823,14 +2827,14 @@
         <v>4</v>
       </c>
       <c r="D47" s="98"/>
-      <c r="E47" s="104" t="s">
+      <c r="E47" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="F47" s="105"/>
-      <c r="G47" s="104" t="s">
+      <c r="F47" s="103"/>
+      <c r="G47" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="H47" s="104"/>
+      <c r="H47" s="105"/>
       <c r="I47" s="15"/>
       <c r="J47" s="16"/>
       <c r="K47" s="9"/>
@@ -2840,10 +2844,10 @@
       <c r="B48" s="97"/>
       <c r="C48" s="96"/>
       <c r="D48" s="99"/>
-      <c r="E48" s="104"/>
-      <c r="F48" s="106"/>
-      <c r="G48" s="104"/>
-      <c r="H48" s="104"/>
+      <c r="E48" s="105"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="105"/>
+      <c r="H48" s="105"/>
       <c r="I48" s="17"/>
       <c r="J48" s="28"/>
       <c r="K48" s="14"/>
@@ -2994,14 +2998,14 @@
         <v>4</v>
       </c>
       <c r="D60" s="98"/>
-      <c r="E60" s="104" t="s">
+      <c r="E60" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="F60" s="105"/>
-      <c r="G60" s="104" t="s">
+      <c r="F60" s="103"/>
+      <c r="G60" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="H60" s="104"/>
+      <c r="H60" s="105"/>
       <c r="I60" s="15"/>
       <c r="J60" s="16"/>
       <c r="K60" s="9"/>
@@ -3011,10 +3015,10 @@
       <c r="B61" s="97"/>
       <c r="C61" s="96"/>
       <c r="D61" s="99"/>
-      <c r="E61" s="104"/>
-      <c r="F61" s="106"/>
-      <c r="G61" s="104"/>
-      <c r="H61" s="104"/>
+      <c r="E61" s="105"/>
+      <c r="F61" s="104"/>
+      <c r="G61" s="105"/>
+      <c r="H61" s="105"/>
       <c r="I61" s="17"/>
       <c r="J61" s="28"/>
       <c r="K61" s="14"/>
@@ -3254,16 +3258,16 @@
       <c r="K80" s="14"/>
     </row>
     <row r="81" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="114" t="s">
+      <c r="A81" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="B81" s="114" t="s">
+      <c r="B81" s="101" t="s">
         <v>3</v>
       </c>
       <c r="C81" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="D81" s="105"/>
+      <c r="D81" s="103"/>
       <c r="E81" s="93" t="s">
         <v>6</v>
       </c>
@@ -3281,10 +3285,10 @@
       <c r="K81" s="9"/>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A82" s="115"/>
-      <c r="B82" s="115"/>
+      <c r="A82" s="102"/>
+      <c r="B82" s="102"/>
       <c r="C82" s="96"/>
-      <c r="D82" s="106"/>
+      <c r="D82" s="104"/>
       <c r="E82" s="94"/>
       <c r="F82" s="94"/>
       <c r="G82" s="94"/>
@@ -3475,17 +3479,17 @@
       <c r="K94" s="14"/>
     </row>
     <row r="95" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="97" t="s">
+      <c r="A95" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="B95" s="97" t="s">
+      <c r="B95" s="101" t="s">
         <v>3</v>
       </c>
       <c r="C95" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="98"/>
-      <c r="E95" s="100" t="s">
+      <c r="D95" s="103"/>
+      <c r="E95" s="93" t="s">
         <v>6</v>
       </c>
       <c r="F95" s="93" t="s">
@@ -3502,11 +3506,11 @@
       <c r="K95" s="9"/>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A96" s="97"/>
-      <c r="B96" s="97"/>
+      <c r="A96" s="102"/>
+      <c r="B96" s="102"/>
       <c r="C96" s="96"/>
-      <c r="D96" s="99"/>
-      <c r="E96" s="100"/>
+      <c r="D96" s="104"/>
+      <c r="E96" s="94"/>
       <c r="F96" s="94"/>
       <c r="G96" s="94"/>
       <c r="H96" s="96"/>
@@ -3519,19 +3523,17 @@
         <v>1</v>
       </c>
       <c r="B97" s="61" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="C97" s="77" t="s">
         <v>47</v>
       </c>
       <c r="D97" s="80"/>
       <c r="E97" s="74"/>
-      <c r="F97" s="59" t="s">
-        <v>14</v>
-      </c>
+      <c r="F97" s="59"/>
       <c r="G97" s="19"/>
       <c r="H97" s="83" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I97" s="20"/>
       <c r="J97" s="27"/>
@@ -3542,34 +3544,38 @@
         <f>A97+1</f>
         <v>2</v>
       </c>
-      <c r="B98" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="C98" s="78" t="s">
-        <v>70</v>
+      <c r="B98" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="C98" s="77" t="s">
+        <v>29</v>
       </c>
       <c r="D98" s="80"/>
       <c r="E98" s="74"/>
       <c r="F98" s="59"/>
       <c r="G98" s="19"/>
-      <c r="H98" s="84" t="s">
-        <v>79</v>
-      </c>
+      <c r="H98" s="84"/>
       <c r="I98" s="20"/>
       <c r="J98" s="27"/>
       <c r="K98" s="14"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="18">
-        <f t="shared" ref="A99:A102" si="4">A98+1</f>
+        <f t="shared" ref="A99:A103" si="4">A98+1</f>
         <v>3</v>
       </c>
-      <c r="B99" s="62"/>
-      <c r="C99" s="78"/>
-      <c r="D99" s="80"/>
+      <c r="B99" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="C99" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D99" s="81"/>
       <c r="E99" s="80"/>
       <c r="F99" s="59"/>
-      <c r="G99" s="19"/>
+      <c r="G99" s="19" t="s">
+        <v>14</v>
+      </c>
       <c r="H99" s="84"/>
       <c r="I99" s="20"/>
       <c r="J99" s="21"/>
@@ -3589,7 +3595,9 @@
       <c r="D100" s="92"/>
       <c r="E100" s="74"/>
       <c r="F100" s="59"/>
-      <c r="G100" s="19"/>
+      <c r="G100" s="19" t="s">
+        <v>14</v>
+      </c>
       <c r="H100" s="84" t="s">
         <v>87</v>
       </c>
@@ -3602,12 +3610,18 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="B101" s="63"/>
-      <c r="C101" s="79"/>
-      <c r="D101" s="80"/>
+      <c r="B101" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="C101" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="D101" s="89"/>
       <c r="E101" s="74"/>
       <c r="F101" s="59"/>
-      <c r="G101" s="19"/>
+      <c r="G101" s="19" t="s">
+        <v>14</v>
+      </c>
       <c r="H101" s="84"/>
       <c r="I101" s="20"/>
       <c r="J101" s="21"/>
@@ -3630,125 +3644,119 @@
       <c r="K102" s="14"/>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A103" s="22"/>
-      <c r="B103" s="23"/>
-      <c r="C103" s="24"/>
-      <c r="D103" s="82"/>
-      <c r="E103" s="76"/>
-      <c r="F103" s="60"/>
-      <c r="G103" s="24"/>
-      <c r="H103" s="86"/>
-      <c r="I103" s="25"/>
-      <c r="J103" s="26"/>
+      <c r="A103" s="18">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="B103" s="63"/>
+      <c r="C103" s="79"/>
+      <c r="D103" s="81"/>
+      <c r="E103" s="75"/>
+      <c r="F103" s="65"/>
+      <c r="G103" s="64"/>
+      <c r="H103" s="85"/>
+      <c r="I103" s="66"/>
+      <c r="J103" s="67"/>
       <c r="K103" s="14"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A106"/>
-      <c r="B106" t="s">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A104" s="22"/>
+      <c r="B104" s="23"/>
+      <c r="C104" s="24"/>
+      <c r="D104" s="82"/>
+      <c r="E104" s="76"/>
+      <c r="F104" s="60"/>
+      <c r="G104" s="24"/>
+      <c r="H104" s="86"/>
+      <c r="I104" s="25"/>
+      <c r="J104" s="26"/>
+      <c r="K104" s="14"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A107"/>
+      <c r="B107" t="s">
         <v>43</v>
       </c>
-      <c r="C106"/>
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
-      <c r="G106"/>
-      <c r="H106"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A107" s="3" t="s">
+      <c r="C107"/>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A108" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B107" s="13"/>
-      <c r="C107" s="13"/>
-      <c r="D107" s="13"/>
-      <c r="E107" s="13"/>
-      <c r="F107" s="13"/>
-      <c r="G107" s="13"/>
-      <c r="H107" s="13"/>
-      <c r="I107" s="13"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="14"/>
-    </row>
-    <row r="108" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="97" t="s">
+      <c r="B108" s="13"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="13"/>
+      <c r="E108" s="13"/>
+      <c r="F108" s="13"/>
+      <c r="G108" s="13"/>
+      <c r="H108" s="13"/>
+      <c r="I108" s="13"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="14"/>
+    </row>
+    <row r="109" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="B108" s="97" t="s">
+      <c r="B109" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="C108" s="95" t="s">
+      <c r="C109" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="98"/>
-      <c r="E108" s="100" t="s">
+      <c r="D109" s="98"/>
+      <c r="E109" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="F108" s="93" t="s">
+      <c r="F109" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="G108" s="93" t="s">
+      <c r="G109" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="H108" s="95" t="s">
+      <c r="H109" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="I108" s="15"/>
-      <c r="J108" s="16"/>
-      <c r="K108" s="9"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A109" s="97"/>
-      <c r="B109" s="97"/>
-      <c r="C109" s="96"/>
-      <c r="D109" s="99"/>
-      <c r="E109" s="100"/>
-      <c r="F109" s="94"/>
-      <c r="G109" s="94"/>
-      <c r="H109" s="96"/>
-      <c r="I109" s="17"/>
-      <c r="J109" s="28"/>
-      <c r="K109" s="14"/>
+      <c r="I109" s="15"/>
+      <c r="J109" s="16"/>
+      <c r="K109" s="9"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A110" s="18">
-        <v>1</v>
-      </c>
-      <c r="B110" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="C110" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="D110" s="80"/>
-      <c r="E110" s="74"/>
-      <c r="F110" s="59"/>
-      <c r="G110" s="19"/>
-      <c r="H110" s="83" t="s">
-        <v>66</v>
-      </c>
-      <c r="I110" s="20"/>
-      <c r="J110" s="27"/>
+      <c r="A110" s="97"/>
+      <c r="B110" s="97"/>
+      <c r="C110" s="96"/>
+      <c r="D110" s="99"/>
+      <c r="E110" s="100"/>
+      <c r="F110" s="94"/>
+      <c r="G110" s="94"/>
+      <c r="H110" s="96"/>
+      <c r="I110" s="17"/>
+      <c r="J110" s="28"/>
       <c r="K110" s="14"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="18">
-        <f>A110+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B111" s="61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C111" s="77" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="D111" s="80"/>
       <c r="E111" s="74"/>
-      <c r="F111" s="59"/>
-      <c r="G111" s="19" t="s">
+      <c r="F111" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="H111" s="84" t="s">
-        <v>65</v>
+      <c r="G111" s="19"/>
+      <c r="H111" s="83" t="s">
+        <v>62</v>
       </c>
       <c r="I111" s="20"/>
       <c r="J111" s="27"/>
@@ -3756,37 +3764,35 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="18">
-        <f t="shared" ref="A112:A115" si="5">A111+1</f>
-        <v>3</v>
-      </c>
-      <c r="B112" s="90" t="s">
-        <v>86</v>
-      </c>
-      <c r="C112" s="91" t="s">
-        <v>29</v>
-      </c>
-      <c r="D112" s="92"/>
+        <f>A111+1</f>
+        <v>2</v>
+      </c>
+      <c r="B112" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="C112" s="78" t="s">
+        <v>70</v>
+      </c>
+      <c r="D112" s="80"/>
       <c r="E112" s="74"/>
       <c r="F112" s="59"/>
-      <c r="G112" s="19" t="s">
-        <v>14</v>
-      </c>
+      <c r="G112" s="19"/>
       <c r="H112" s="84" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I112" s="20"/>
-      <c r="J112" s="21"/>
+      <c r="J112" s="27"/>
       <c r="K112" s="14"/>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="18">
-        <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="B113" s="63"/>
-      <c r="C113" s="79"/>
+        <f t="shared" ref="A113:A116" si="5">A112+1</f>
+        <v>3</v>
+      </c>
+      <c r="B113" s="62"/>
+      <c r="C113" s="78"/>
       <c r="D113" s="80"/>
-      <c r="E113" s="74"/>
+      <c r="E113" s="80"/>
       <c r="F113" s="59"/>
       <c r="G113" s="19"/>
       <c r="H113" s="84"/>
@@ -3797,15 +3803,21 @@
     <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="18">
         <f t="shared" si="5"/>
-        <v>5</v>
-      </c>
-      <c r="B114" s="63"/>
-      <c r="C114" s="79"/>
-      <c r="D114" s="80"/>
+        <v>4</v>
+      </c>
+      <c r="B114" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="C114" s="91" t="s">
+        <v>29</v>
+      </c>
+      <c r="D114" s="92"/>
       <c r="E114" s="74"/>
       <c r="F114" s="59"/>
       <c r="G114" s="19"/>
-      <c r="H114" s="84"/>
+      <c r="H114" s="84" t="s">
+        <v>87</v>
+      </c>
       <c r="I114" s="20"/>
       <c r="J114" s="21"/>
       <c r="K114" s="14"/>
@@ -3813,139 +3825,131 @@
     <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="18">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B115" s="63"/>
       <c r="C115" s="79"/>
-      <c r="D115" s="81"/>
-      <c r="E115" s="75"/>
-      <c r="F115" s="65"/>
-      <c r="G115" s="64"/>
-      <c r="H115" s="85"/>
-      <c r="I115" s="66"/>
-      <c r="J115" s="67"/>
+      <c r="D115" s="80"/>
+      <c r="E115" s="74"/>
+      <c r="F115" s="59"/>
+      <c r="G115" s="19"/>
+      <c r="H115" s="84"/>
+      <c r="I115" s="20"/>
+      <c r="J115" s="21"/>
       <c r="K115" s="14"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A116" s="22"/>
-      <c r="B116" s="23"/>
-      <c r="C116" s="24"/>
-      <c r="D116" s="82"/>
-      <c r="E116" s="76"/>
-      <c r="F116" s="60"/>
-      <c r="G116" s="24"/>
-      <c r="H116" s="86"/>
-      <c r="I116" s="25"/>
-      <c r="J116" s="26"/>
+      <c r="A116" s="18">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="B116" s="63"/>
+      <c r="C116" s="79"/>
+      <c r="D116" s="81"/>
+      <c r="E116" s="75"/>
+      <c r="F116" s="65"/>
+      <c r="G116" s="64"/>
+      <c r="H116" s="85"/>
+      <c r="I116" s="66"/>
+      <c r="J116" s="67"/>
       <c r="K116" s="14"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A119"/>
-      <c r="B119" t="s">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A117" s="22"/>
+      <c r="B117" s="23"/>
+      <c r="C117" s="24"/>
+      <c r="D117" s="82"/>
+      <c r="E117" s="76"/>
+      <c r="F117" s="60"/>
+      <c r="G117" s="24"/>
+      <c r="H117" s="86"/>
+      <c r="I117" s="25"/>
+      <c r="J117" s="26"/>
+      <c r="K117" s="14"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A120"/>
+      <c r="B120" t="s">
         <v>43</v>
       </c>
-      <c r="C119"/>
-      <c r="D119"/>
-      <c r="E119"/>
-      <c r="F119"/>
-      <c r="G119"/>
-      <c r="H119"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A120" s="3" t="s">
+      <c r="C120"/>
+      <c r="D120"/>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="G120"/>
+      <c r="H120"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A121" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B120" s="13"/>
-      <c r="C120" s="13"/>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
-      <c r="F120" s="13"/>
-      <c r="G120" s="13"/>
-      <c r="H120" s="13"/>
-      <c r="I120" s="13"/>
-      <c r="J120" s="6"/>
-      <c r="K120" s="14"/>
-    </row>
-    <row r="121" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="97" t="s">
+      <c r="B121" s="13"/>
+      <c r="C121" s="13"/>
+      <c r="D121" s="13"/>
+      <c r="E121" s="13"/>
+      <c r="F121" s="13"/>
+      <c r="G121" s="13"/>
+      <c r="H121" s="13"/>
+      <c r="I121" s="13"/>
+      <c r="J121" s="6"/>
+      <c r="K121" s="14"/>
+    </row>
+    <row r="122" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="B121" s="97" t="s">
+      <c r="B122" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="C121" s="95" t="s">
+      <c r="C122" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="D121" s="98"/>
-      <c r="E121" s="100" t="s">
+      <c r="D122" s="98"/>
+      <c r="E122" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="F121" s="93" t="s">
+      <c r="F122" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="G121" s="93" t="s">
+      <c r="G122" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="H121" s="95" t="s">
+      <c r="H122" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="I121" s="15"/>
-      <c r="J121" s="16"/>
-      <c r="K121" s="9"/>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A122" s="97"/>
-      <c r="B122" s="97"/>
-      <c r="C122" s="96"/>
-      <c r="D122" s="99"/>
-      <c r="E122" s="100"/>
-      <c r="F122" s="94"/>
-      <c r="G122" s="94"/>
-      <c r="H122" s="96"/>
-      <c r="I122" s="17"/>
-      <c r="J122" s="28"/>
-      <c r="K122" s="14"/>
+      <c r="I122" s="15"/>
+      <c r="J122" s="16"/>
+      <c r="K122" s="9"/>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A123" s="18">
-        <v>1</v>
-      </c>
-      <c r="B123" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="C123" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="D123" s="80"/>
-      <c r="E123" s="74"/>
-      <c r="F123" s="59" t="s">
-        <v>14</v>
-      </c>
-      <c r="G123" s="19"/>
-      <c r="H123" s="83" t="s">
-        <v>77</v>
-      </c>
-      <c r="I123" s="20"/>
-      <c r="J123" s="27"/>
+      <c r="A123" s="97"/>
+      <c r="B123" s="97"/>
+      <c r="C123" s="96"/>
+      <c r="D123" s="99"/>
+      <c r="E123" s="100"/>
+      <c r="F123" s="94"/>
+      <c r="G123" s="94"/>
+      <c r="H123" s="96"/>
+      <c r="I123" s="17"/>
+      <c r="J123" s="28"/>
       <c r="K123" s="14"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="18">
-        <f>A123+1</f>
-        <v>2</v>
-      </c>
-      <c r="B124" s="90" t="s">
-        <v>86</v>
-      </c>
-      <c r="C124" s="91" t="s">
-        <v>29</v>
-      </c>
-      <c r="D124" s="92"/>
+        <v>1</v>
+      </c>
+      <c r="B124" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="C124" s="77" t="s">
+        <v>47</v>
+      </c>
+      <c r="D124" s="80"/>
       <c r="E124" s="74"/>
       <c r="F124" s="59"/>
       <c r="G124" s="19"/>
-      <c r="H124" s="84" t="s">
-        <v>87</v>
+      <c r="H124" s="83" t="s">
+        <v>66</v>
       </c>
       <c r="I124" s="20"/>
       <c r="J124" s="27"/>
@@ -3953,32 +3957,48 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="18">
-        <f t="shared" ref="A125:A128" si="6">A124+1</f>
-        <v>3</v>
-      </c>
-      <c r="B125" s="62"/>
-      <c r="C125" s="78"/>
+        <f>A124+1</f>
+        <v>2</v>
+      </c>
+      <c r="B125" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="C125" s="77" t="s">
+        <v>82</v>
+      </c>
       <c r="D125" s="80"/>
-      <c r="E125" s="80"/>
+      <c r="E125" s="74"/>
       <c r="F125" s="59"/>
-      <c r="G125" s="19"/>
-      <c r="H125" s="84"/>
+      <c r="G125" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H125" s="84" t="s">
+        <v>65</v>
+      </c>
       <c r="I125" s="20"/>
-      <c r="J125" s="21"/>
+      <c r="J125" s="27"/>
       <c r="K125" s="14"/>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="18">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="B126" s="63"/>
-      <c r="C126" s="79"/>
-      <c r="D126" s="80"/>
+        <f t="shared" ref="A126:A129" si="6">A125+1</f>
+        <v>3</v>
+      </c>
+      <c r="B126" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="C126" s="91" t="s">
+        <v>29</v>
+      </c>
+      <c r="D126" s="92"/>
       <c r="E126" s="74"/>
       <c r="F126" s="59"/>
-      <c r="G126" s="19"/>
-      <c r="H126" s="84"/>
+      <c r="G126" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H126" s="84" t="s">
+        <v>87</v>
+      </c>
       <c r="I126" s="20"/>
       <c r="J126" s="21"/>
       <c r="K126" s="14"/>
@@ -3986,7 +4006,7 @@
     <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="18">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B127" s="63"/>
       <c r="C127" s="79"/>
@@ -4002,137 +4022,133 @@
     <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="18">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B128" s="63"/>
       <c r="C128" s="79"/>
-      <c r="D128" s="81"/>
-      <c r="E128" s="75"/>
-      <c r="F128" s="65"/>
-      <c r="G128" s="64"/>
-      <c r="H128" s="85"/>
-      <c r="I128" s="66"/>
-      <c r="J128" s="67"/>
+      <c r="D128" s="80"/>
+      <c r="E128" s="74"/>
+      <c r="F128" s="59"/>
+      <c r="G128" s="19"/>
+      <c r="H128" s="84"/>
+      <c r="I128" s="20"/>
+      <c r="J128" s="21"/>
       <c r="K128" s="14"/>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A129" s="22"/>
-      <c r="B129" s="23"/>
-      <c r="C129" s="24"/>
-      <c r="D129" s="82"/>
-      <c r="E129" s="76"/>
-      <c r="F129" s="60"/>
-      <c r="G129" s="24"/>
-      <c r="H129" s="86"/>
-      <c r="I129" s="25"/>
-      <c r="J129" s="26"/>
+      <c r="A129" s="18">
+        <f t="shared" si="6"/>
+        <v>6</v>
+      </c>
+      <c r="B129" s="63"/>
+      <c r="C129" s="79"/>
+      <c r="D129" s="81"/>
+      <c r="E129" s="75"/>
+      <c r="F129" s="65"/>
+      <c r="G129" s="64"/>
+      <c r="H129" s="85"/>
+      <c r="I129" s="66"/>
+      <c r="J129" s="67"/>
       <c r="K129" s="14"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A132"/>
-      <c r="B132" t="s">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A130" s="22"/>
+      <c r="B130" s="23"/>
+      <c r="C130" s="24"/>
+      <c r="D130" s="82"/>
+      <c r="E130" s="76"/>
+      <c r="F130" s="60"/>
+      <c r="G130" s="24"/>
+      <c r="H130" s="86"/>
+      <c r="I130" s="25"/>
+      <c r="J130" s="26"/>
+      <c r="K130" s="14"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A133"/>
+      <c r="B133" t="s">
         <v>43</v>
       </c>
-      <c r="C132"/>
-      <c r="D132"/>
-      <c r="E132"/>
-      <c r="F132"/>
-      <c r="G132"/>
-      <c r="H132"/>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A133" s="3" t="s">
+      <c r="C133"/>
+      <c r="D133"/>
+      <c r="E133"/>
+      <c r="F133"/>
+      <c r="G133"/>
+      <c r="H133"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A134" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B133" s="13"/>
-      <c r="C133" s="13"/>
-      <c r="D133" s="13"/>
-      <c r="E133" s="13"/>
-      <c r="F133" s="13"/>
-      <c r="G133" s="13"/>
-      <c r="H133" s="13"/>
-      <c r="I133" s="13"/>
-      <c r="J133" s="6"/>
-      <c r="K133" s="14"/>
-    </row>
-    <row r="134" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="97" t="s">
+      <c r="B134" s="13"/>
+      <c r="C134" s="13"/>
+      <c r="D134" s="13"/>
+      <c r="E134" s="13"/>
+      <c r="F134" s="13"/>
+      <c r="G134" s="13"/>
+      <c r="H134" s="13"/>
+      <c r="I134" s="13"/>
+      <c r="J134" s="6"/>
+      <c r="K134" s="14"/>
+    </row>
+    <row r="135" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="B134" s="97" t="s">
+      <c r="B135" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="C134" s="95" t="s">
+      <c r="C135" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="D134" s="98"/>
-      <c r="E134" s="100" t="s">
+      <c r="D135" s="98"/>
+      <c r="E135" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="F134" s="93" t="s">
+      <c r="F135" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="G134" s="93" t="s">
+      <c r="G135" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="H134" s="95" t="s">
+      <c r="H135" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="I134" s="15"/>
-      <c r="J134" s="16"/>
-      <c r="K134" s="9"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A135" s="97"/>
-      <c r="B135" s="97"/>
-      <c r="C135" s="96"/>
-      <c r="D135" s="99"/>
-      <c r="E135" s="100"/>
-      <c r="F135" s="94"/>
-      <c r="G135" s="94"/>
-      <c r="H135" s="96"/>
-      <c r="I135" s="17"/>
-      <c r="J135" s="28"/>
-      <c r="K135" s="14"/>
+      <c r="I135" s="15"/>
+      <c r="J135" s="16"/>
+      <c r="K135" s="9"/>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A136" s="18">
-        <v>1</v>
-      </c>
-      <c r="B136" s="61" t="s">
-        <v>78</v>
-      </c>
-      <c r="C136" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="D136" s="80"/>
-      <c r="E136" s="74"/>
-      <c r="F136" s="59"/>
-      <c r="G136" s="19"/>
-      <c r="H136" s="83" t="s">
-        <v>81</v>
-      </c>
-      <c r="I136" s="20"/>
-      <c r="J136" s="27"/>
+      <c r="A136" s="97"/>
+      <c r="B136" s="97"/>
+      <c r="C136" s="96"/>
+      <c r="D136" s="99"/>
+      <c r="E136" s="100"/>
+      <c r="F136" s="94"/>
+      <c r="G136" s="94"/>
+      <c r="H136" s="96"/>
+      <c r="I136" s="17"/>
+      <c r="J136" s="28"/>
       <c r="K136" s="14"/>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="18">
-        <f>A136+1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B137" s="61" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C137" s="77" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D137" s="80"/>
       <c r="E137" s="74"/>
-      <c r="F137" s="59"/>
+      <c r="F137" s="59" t="s">
+        <v>14</v>
+      </c>
       <c r="G137" s="19"/>
-      <c r="H137" s="84" t="s">
-        <v>80</v>
+      <c r="H137" s="83" t="s">
+        <v>77</v>
       </c>
       <c r="I137" s="20"/>
       <c r="J137" s="27"/>
@@ -4140,8 +4156,8 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="18">
-        <f t="shared" ref="A138:A141" si="7">A137+1</f>
-        <v>3</v>
+        <f>A137+1</f>
+        <v>2</v>
       </c>
       <c r="B138" s="90" t="s">
         <v>86</v>
@@ -4157,18 +4173,18 @@
         <v>87</v>
       </c>
       <c r="I138" s="20"/>
-      <c r="J138" s="21"/>
+      <c r="J138" s="27"/>
       <c r="K138" s="14"/>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="18">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="B139" s="63"/>
-      <c r="C139" s="79"/>
+        <f t="shared" ref="A139:A142" si="7">A138+1</f>
+        <v>3</v>
+      </c>
+      <c r="B139" s="62"/>
+      <c r="C139" s="78"/>
       <c r="D139" s="80"/>
-      <c r="E139" s="74"/>
+      <c r="E139" s="80"/>
       <c r="F139" s="59"/>
       <c r="G139" s="19"/>
       <c r="H139" s="84"/>
@@ -4179,7 +4195,7 @@
     <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="18">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B140" s="63"/>
       <c r="C140" s="79"/>
@@ -4195,137 +4211,131 @@
     <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="18">
         <f t="shared" si="7"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B141" s="63"/>
       <c r="C141" s="79"/>
-      <c r="D141" s="81"/>
-      <c r="E141" s="75"/>
-      <c r="F141" s="65"/>
-      <c r="G141" s="64"/>
-      <c r="H141" s="85"/>
-      <c r="I141" s="66"/>
-      <c r="J141" s="67"/>
+      <c r="D141" s="80"/>
+      <c r="E141" s="74"/>
+      <c r="F141" s="59"/>
+      <c r="G141" s="19"/>
+      <c r="H141" s="84"/>
+      <c r="I141" s="20"/>
+      <c r="J141" s="21"/>
       <c r="K141" s="14"/>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A142" s="22"/>
-      <c r="B142" s="23"/>
-      <c r="C142" s="24"/>
-      <c r="D142" s="82"/>
-      <c r="E142" s="76"/>
-      <c r="F142" s="60"/>
-      <c r="G142" s="24"/>
-      <c r="H142" s="86"/>
-      <c r="I142" s="25"/>
-      <c r="J142" s="26"/>
+      <c r="A142" s="18">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="B142" s="63"/>
+      <c r="C142" s="79"/>
+      <c r="D142" s="81"/>
+      <c r="E142" s="75"/>
+      <c r="F142" s="65"/>
+      <c r="G142" s="64"/>
+      <c r="H142" s="85"/>
+      <c r="I142" s="66"/>
+      <c r="J142" s="67"/>
       <c r="K142" s="14"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A145"/>
-      <c r="B145" t="s">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A143" s="22"/>
+      <c r="B143" s="23"/>
+      <c r="C143" s="24"/>
+      <c r="D143" s="82"/>
+      <c r="E143" s="76"/>
+      <c r="F143" s="60"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="86"/>
+      <c r="I143" s="25"/>
+      <c r="J143" s="26"/>
+      <c r="K143" s="14"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A146"/>
+      <c r="B146" t="s">
         <v>43</v>
       </c>
-      <c r="C145"/>
-      <c r="D145"/>
-      <c r="E145"/>
-      <c r="F145"/>
-      <c r="G145"/>
-      <c r="H145"/>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A146" s="3" t="s">
+      <c r="C146"/>
+      <c r="D146"/>
+      <c r="E146"/>
+      <c r="F146"/>
+      <c r="G146"/>
+      <c r="H146"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B146" s="13"/>
-      <c r="C146" s="13"/>
-      <c r="D146" s="13"/>
-      <c r="E146" s="13"/>
-      <c r="F146" s="13"/>
-      <c r="G146" s="13"/>
-      <c r="H146" s="13"/>
-      <c r="I146" s="13"/>
-      <c r="J146" s="6"/>
-      <c r="K146" s="14"/>
-    </row>
-    <row r="147" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="97" t="s">
+      <c r="B147" s="13"/>
+      <c r="C147" s="13"/>
+      <c r="D147" s="13"/>
+      <c r="E147" s="13"/>
+      <c r="F147" s="13"/>
+      <c r="G147" s="13"/>
+      <c r="H147" s="13"/>
+      <c r="I147" s="13"/>
+      <c r="J147" s="6"/>
+      <c r="K147" s="14"/>
+    </row>
+    <row r="148" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="B147" s="97" t="s">
+      <c r="B148" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="C147" s="95" t="s">
+      <c r="C148" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="98"/>
-      <c r="E147" s="100" t="s">
+      <c r="D148" s="98"/>
+      <c r="E148" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="F147" s="93" t="s">
+      <c r="F148" s="93" t="s">
         <v>48</v>
       </c>
-      <c r="G147" s="93" t="s">
+      <c r="G148" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="H147" s="95" t="s">
+      <c r="H148" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="I147" s="15"/>
-      <c r="J147" s="16"/>
-      <c r="K147" s="9"/>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A148" s="97"/>
-      <c r="B148" s="97"/>
-      <c r="C148" s="96"/>
-      <c r="D148" s="99"/>
-      <c r="E148" s="100"/>
-      <c r="F148" s="94"/>
-      <c r="G148" s="94"/>
-      <c r="H148" s="96"/>
-      <c r="I148" s="17"/>
-      <c r="J148" s="28"/>
-      <c r="K148" s="14"/>
+      <c r="I148" s="15"/>
+      <c r="J148" s="16"/>
+      <c r="K148" s="9"/>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A149" s="18">
-        <v>1</v>
-      </c>
-      <c r="B149" s="61" t="s">
-        <v>88</v>
-      </c>
-      <c r="C149" s="77" t="s">
-        <v>47</v>
-      </c>
-      <c r="D149" s="80"/>
-      <c r="E149" s="74"/>
-      <c r="F149" s="59"/>
-      <c r="G149" s="19"/>
-      <c r="H149" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="I149" s="20"/>
-      <c r="J149" s="27"/>
+      <c r="A149" s="97"/>
+      <c r="B149" s="97"/>
+      <c r="C149" s="96"/>
+      <c r="D149" s="99"/>
+      <c r="E149" s="100"/>
+      <c r="F149" s="94"/>
+      <c r="G149" s="94"/>
+      <c r="H149" s="96"/>
+      <c r="I149" s="17"/>
+      <c r="J149" s="28"/>
       <c r="K149" s="14"/>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" s="18">
-        <f>A149+1</f>
-        <v>2</v>
-      </c>
-      <c r="B150" s="90" t="s">
-        <v>86</v>
-      </c>
-      <c r="C150" s="91" t="s">
-        <v>29</v>
-      </c>
-      <c r="D150" s="92"/>
+        <v>1</v>
+      </c>
+      <c r="B150" s="61" t="s">
+        <v>78</v>
+      </c>
+      <c r="C150" s="77" t="s">
+        <v>47</v>
+      </c>
+      <c r="D150" s="80"/>
       <c r="E150" s="74"/>
       <c r="F150" s="59"/>
       <c r="G150" s="19"/>
-      <c r="H150" s="84" t="s">
-        <v>87</v>
+      <c r="H150" s="83" t="s">
+        <v>81</v>
       </c>
       <c r="I150" s="20"/>
       <c r="J150" s="27"/>
@@ -4333,32 +4343,44 @@
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" s="18">
-        <f t="shared" ref="A151:A154" si="8">A150+1</f>
-        <v>3</v>
-      </c>
-      <c r="B151" s="90"/>
-      <c r="C151" s="91"/>
-      <c r="D151" s="92"/>
+        <f>A150+1</f>
+        <v>2</v>
+      </c>
+      <c r="B151" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="C151" s="77" t="s">
+        <v>29</v>
+      </c>
+      <c r="D151" s="80"/>
       <c r="E151" s="74"/>
       <c r="F151" s="59"/>
       <c r="G151" s="19"/>
-      <c r="H151" s="84"/>
+      <c r="H151" s="84" t="s">
+        <v>80</v>
+      </c>
       <c r="I151" s="20"/>
-      <c r="J151" s="21"/>
+      <c r="J151" s="27"/>
       <c r="K151" s="14"/>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" s="18">
-        <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-      <c r="B152" s="63"/>
-      <c r="C152" s="79"/>
-      <c r="D152" s="80"/>
+        <f t="shared" ref="A152:A155" si="8">A151+1</f>
+        <v>3</v>
+      </c>
+      <c r="B152" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="C152" s="91" t="s">
+        <v>29</v>
+      </c>
+      <c r="D152" s="92"/>
       <c r="E152" s="74"/>
       <c r="F152" s="59"/>
       <c r="G152" s="19"/>
-      <c r="H152" s="84"/>
+      <c r="H152" s="84" t="s">
+        <v>87</v>
+      </c>
       <c r="I152" s="20"/>
       <c r="J152" s="21"/>
       <c r="K152" s="14"/>
@@ -4366,7 +4388,7 @@
     <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" s="18">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B153" s="63"/>
       <c r="C153" s="79"/>
@@ -4382,66 +4404,262 @@
     <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" s="18">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B154" s="63"/>
       <c r="C154" s="79"/>
-      <c r="D154" s="81"/>
-      <c r="E154" s="75"/>
-      <c r="F154" s="65"/>
-      <c r="G154" s="64"/>
-      <c r="H154" s="85"/>
-      <c r="I154" s="66"/>
-      <c r="J154" s="67"/>
+      <c r="D154" s="80"/>
+      <c r="E154" s="74"/>
+      <c r="F154" s="59"/>
+      <c r="G154" s="19"/>
+      <c r="H154" s="84"/>
+      <c r="I154" s="20"/>
+      <c r="J154" s="21"/>
       <c r="K154" s="14"/>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A155" s="22"/>
-      <c r="B155" s="23"/>
-      <c r="C155" s="24"/>
-      <c r="D155" s="82"/>
-      <c r="E155" s="76"/>
-      <c r="F155" s="60"/>
-      <c r="G155" s="24"/>
-      <c r="H155" s="86"/>
-      <c r="I155" s="25"/>
-      <c r="J155" s="26"/>
+      <c r="A155" s="18">
+        <f t="shared" si="8"/>
+        <v>6</v>
+      </c>
+      <c r="B155" s="63"/>
+      <c r="C155" s="79"/>
+      <c r="D155" s="81"/>
+      <c r="E155" s="75"/>
+      <c r="F155" s="65"/>
+      <c r="G155" s="64"/>
+      <c r="H155" s="85"/>
+      <c r="I155" s="66"/>
+      <c r="J155" s="67"/>
       <c r="K155" s="14"/>
     </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A156" s="22"/>
+      <c r="B156" s="23"/>
+      <c r="C156" s="24"/>
+      <c r="D156" s="82"/>
+      <c r="E156" s="76"/>
+      <c r="F156" s="60"/>
+      <c r="G156" s="24"/>
+      <c r="H156" s="86"/>
+      <c r="I156" s="25"/>
+      <c r="J156" s="26"/>
+      <c r="K156" s="14"/>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A159"/>
+      <c r="B159" t="s">
+        <v>43</v>
+      </c>
+      <c r="C159"/>
+      <c r="D159"/>
+      <c r="E159"/>
+      <c r="F159"/>
+      <c r="G159"/>
+      <c r="H159"/>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A160" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B160" s="13"/>
+      <c r="C160" s="13"/>
+      <c r="D160" s="13"/>
+      <c r="E160" s="13"/>
+      <c r="F160" s="13"/>
+      <c r="G160" s="13"/>
+      <c r="H160" s="13"/>
+      <c r="I160" s="13"/>
+      <c r="J160" s="6"/>
+      <c r="K160" s="14"/>
+    </row>
+    <row r="161" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="97" t="s">
+        <v>7</v>
+      </c>
+      <c r="B161" s="97" t="s">
+        <v>3</v>
+      </c>
+      <c r="C161" s="95" t="s">
+        <v>4</v>
+      </c>
+      <c r="D161" s="98"/>
+      <c r="E161" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="F161" s="93" t="s">
+        <v>48</v>
+      </c>
+      <c r="G161" s="93" t="s">
+        <v>40</v>
+      </c>
+      <c r="H161" s="95" t="s">
+        <v>1</v>
+      </c>
+      <c r="I161" s="15"/>
+      <c r="J161" s="16"/>
+      <c r="K161" s="9"/>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A162" s="97"/>
+      <c r="B162" s="97"/>
+      <c r="C162" s="96"/>
+      <c r="D162" s="99"/>
+      <c r="E162" s="100"/>
+      <c r="F162" s="94"/>
+      <c r="G162" s="94"/>
+      <c r="H162" s="96"/>
+      <c r="I162" s="17"/>
+      <c r="J162" s="28"/>
+      <c r="K162" s="14"/>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A163" s="18">
+        <v>1</v>
+      </c>
+      <c r="B163" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="C163" s="77" t="s">
+        <v>47</v>
+      </c>
+      <c r="D163" s="80"/>
+      <c r="E163" s="74"/>
+      <c r="F163" s="59"/>
+      <c r="G163" s="19"/>
+      <c r="H163" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="I163" s="20"/>
+      <c r="J163" s="27"/>
+      <c r="K163" s="14"/>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A164" s="18">
+        <f>A163+1</f>
+        <v>2</v>
+      </c>
+      <c r="B164" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="C164" s="91" t="s">
+        <v>29</v>
+      </c>
+      <c r="D164" s="92"/>
+      <c r="E164" s="74"/>
+      <c r="F164" s="59"/>
+      <c r="G164" s="19"/>
+      <c r="H164" s="84" t="s">
+        <v>87</v>
+      </c>
+      <c r="I164" s="20"/>
+      <c r="J164" s="27"/>
+      <c r="K164" s="14"/>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A165" s="18">
+        <f t="shared" ref="A165:A168" si="9">A164+1</f>
+        <v>3</v>
+      </c>
+      <c r="B165" s="90"/>
+      <c r="C165" s="91"/>
+      <c r="D165" s="92"/>
+      <c r="E165" s="74"/>
+      <c r="F165" s="59"/>
+      <c r="G165" s="19"/>
+      <c r="H165" s="84"/>
+      <c r="I165" s="20"/>
+      <c r="J165" s="21"/>
+      <c r="K165" s="14"/>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A166" s="18">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="B166" s="63"/>
+      <c r="C166" s="79"/>
+      <c r="D166" s="80"/>
+      <c r="E166" s="74"/>
+      <c r="F166" s="59"/>
+      <c r="G166" s="19"/>
+      <c r="H166" s="84"/>
+      <c r="I166" s="20"/>
+      <c r="J166" s="21"/>
+      <c r="K166" s="14"/>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A167" s="18">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="B167" s="63"/>
+      <c r="C167" s="79"/>
+      <c r="D167" s="80"/>
+      <c r="E167" s="74"/>
+      <c r="F167" s="59"/>
+      <c r="G167" s="19"/>
+      <c r="H167" s="84"/>
+      <c r="I167" s="20"/>
+      <c r="J167" s="21"/>
+      <c r="K167" s="14"/>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A168" s="18">
+        <f t="shared" si="9"/>
+        <v>6</v>
+      </c>
+      <c r="B168" s="63"/>
+      <c r="C168" s="79"/>
+      <c r="D168" s="81"/>
+      <c r="E168" s="75"/>
+      <c r="F168" s="65"/>
+      <c r="G168" s="64"/>
+      <c r="H168" s="85"/>
+      <c r="I168" s="66"/>
+      <c r="J168" s="67"/>
+      <c r="K168" s="14"/>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A169" s="22"/>
+      <c r="B169" s="23"/>
+      <c r="C169" s="24"/>
+      <c r="D169" s="82"/>
+      <c r="E169" s="76"/>
+      <c r="F169" s="60"/>
+      <c r="G169" s="24"/>
+      <c r="H169" s="86"/>
+      <c r="I169" s="25"/>
+      <c r="J169" s="26"/>
+      <c r="K169" s="14"/>
+    </row>
   </sheetData>
-  <mergeCells count="66">
-    <mergeCell ref="G147:G148"/>
-    <mergeCell ref="H147:H148"/>
-    <mergeCell ref="A147:A148"/>
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="C147:D148"/>
-    <mergeCell ref="E147:E148"/>
-    <mergeCell ref="F147:F148"/>
-    <mergeCell ref="G81:G82"/>
-    <mergeCell ref="H81:H82"/>
+  <mergeCells count="73">
     <mergeCell ref="G95:G96"/>
     <mergeCell ref="H95:H96"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:D109"/>
-    <mergeCell ref="E108:E109"/>
-    <mergeCell ref="F108:F109"/>
-    <mergeCell ref="G108:G109"/>
-    <mergeCell ref="H108:H109"/>
-    <mergeCell ref="A81:A82"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:D82"/>
-    <mergeCell ref="E81:E82"/>
-    <mergeCell ref="F81:F82"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:D96"/>
-    <mergeCell ref="E95:E96"/>
-    <mergeCell ref="F95:F96"/>
+    <mergeCell ref="G148:G149"/>
+    <mergeCell ref="H148:H149"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:D149"/>
+    <mergeCell ref="E148:E149"/>
+    <mergeCell ref="F148:F149"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="A135:A136"/>
+    <mergeCell ref="B135:B136"/>
+    <mergeCell ref="C135:D136"/>
+    <mergeCell ref="E135:E136"/>
+    <mergeCell ref="F135:F136"/>
+    <mergeCell ref="G135:G136"/>
+    <mergeCell ref="H135:H136"/>
+    <mergeCell ref="G47:H48"/>
+    <mergeCell ref="G60:H61"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="C47:D48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="A60:A61"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C10:E10"/>
@@ -4453,29 +4671,43 @@
     <mergeCell ref="E25:E26"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="C121:D122"/>
-    <mergeCell ref="E121:E122"/>
-    <mergeCell ref="F121:F122"/>
-    <mergeCell ref="G121:G122"/>
-    <mergeCell ref="H121:H122"/>
-    <mergeCell ref="G47:H48"/>
-    <mergeCell ref="G60:H61"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="C47:D48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="G134:G135"/>
-    <mergeCell ref="H134:H135"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="B134:B135"/>
-    <mergeCell ref="C134:D135"/>
-    <mergeCell ref="E134:E135"/>
-    <mergeCell ref="F134:F135"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:D110"/>
+    <mergeCell ref="E109:E110"/>
+    <mergeCell ref="F109:F110"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:D96"/>
+    <mergeCell ref="E95:E96"/>
+    <mergeCell ref="F95:F96"/>
+    <mergeCell ref="G81:G82"/>
+    <mergeCell ref="H81:H82"/>
+    <mergeCell ref="G109:G110"/>
+    <mergeCell ref="H109:H110"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="C122:D123"/>
+    <mergeCell ref="E122:E123"/>
+    <mergeCell ref="F122:F123"/>
+    <mergeCell ref="G122:G123"/>
+    <mergeCell ref="H122:H123"/>
+    <mergeCell ref="A81:A82"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:D82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="F81:F82"/>
+    <mergeCell ref="G161:G162"/>
+    <mergeCell ref="H161:H162"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="C161:D162"/>
+    <mergeCell ref="E161:E162"/>
+    <mergeCell ref="F161:F162"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <dataValidations count="3">
@@ -4485,7 +4717,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{CCFC1331-CEEF-574E-9BCC-37D38F486896}">
       <formula1>adjustFieldName</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F97:G103 F149:G155 F123:G129 F110:G116 F136:G142 F83:G90 F27:F35" xr:uid="{18C70D90-9F1A-D84D-9F1C-490DE84E2C64}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F111:G117 F163:G169 F137:G143 F124:G130 F150:G156 F83:G90 F27:F35 F97:G104" xr:uid="{18C70D90-9F1A-D84D-9F1C-490DE84E2C64}">
       <formula1>yesNo</formula1>
     </dataValidation>
   </dataValidations>
